--- a/src/test/resources/FocomplaintData.xlsx
+++ b/src/test/resources/FocomplaintData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation_Project\Automation-Testing-Project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B1530CE-8E4F-4A34-B75C-6D21E08966B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4865A33B-D022-4CBF-A920-14D22391DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FBDC2C50-69D5-436D-8405-2BD5E4038E4C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{FBDC2C50-69D5-436D-8405-2BD5E4038E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>complainttype</t>
   </si>
@@ -66,6 +67,42 @@
   </si>
   <si>
     <t>Delay issue</t>
+  </si>
+  <si>
+    <t>Aman Barma</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Shift</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot </t>
+  </si>
+  <si>
+    <t>Amit Singh (9009)</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>10:00 AM - 12:30 PM</t>
+  </si>
+  <si>
+    <t>05/18/2026 12:25 PM</t>
+  </si>
+  <si>
+    <t>AppointmentDate</t>
   </si>
 </sst>
 </file>
@@ -491,4 +528,99 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34509EAC-7FDF-41E5-8B2C-4BCB0F8BFB1C}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/FocomplaintData.xlsx
+++ b/src/test/resources/FocomplaintData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4865A33B-D022-4CBF-A920-14D22391DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{FBDC2C50-69D5-436D-8405-2BD5E4038E4C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FBDC2C50-69D5-436D-8405-2BD5E4038E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
